--- a/GeoMIP/results/validacion_asimetrico_fuerza_bruta.xlsx
+++ b/GeoMIP/results/validacion_asimetrico_fuerza_bruta.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,102 +417,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n_fut</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_pres</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>m_pool</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>stirling_esperado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>count_rgs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>count_bf</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>phi_rgs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>phi_bf</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>phi_geo</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>phi_sim_k2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>delta_phi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>count_ok</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>sets_ok</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>phi_ok</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>geo_ok</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>t_rgs_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>t_bf_s</t>
         </is>
@@ -588,10 +576,10 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.015045</v>
+        <v>0.018648</v>
       </c>
       <c r="T2" t="n">
-        <v>0.016357</v>
+        <v>0.017518</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +638,10 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.037589</v>
+        <v>0.05859</v>
       </c>
       <c r="T3" t="n">
-        <v>0.037966</v>
+        <v>0.053841</v>
       </c>
     </row>
     <row r="4">
@@ -712,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.022939</v>
+        <v>0.032382</v>
       </c>
       <c r="T4" t="n">
-        <v>0.022293</v>
+        <v>0.036402</v>
       </c>
     </row>
     <row r="5">
@@ -774,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004466</v>
+        <v>0.010305</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007385</v>
+        <v>0.012502</v>
       </c>
     </row>
     <row r="6">
@@ -838,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.004767</v>
+        <v>0.006555</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004449</v>
+        <v>0.005372</v>
       </c>
     </row>
     <row r="7">
@@ -900,10 +888,10 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006228</v>
+        <v>0.009148</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006836</v>
+        <v>0.010148</v>
       </c>
     </row>
     <row r="8">
@@ -962,10 +950,10 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002585</v>
+        <v>0.004131</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002364</v>
+        <v>0.003382</v>
       </c>
     </row>
     <row r="9">
@@ -1024,10 +1012,10 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.000211</v>
+        <v>0.000312</v>
       </c>
       <c r="T9" t="n">
-        <v>0.000745</v>
+        <v>0.001314</v>
       </c>
     </row>
     <row r="10">
@@ -1088,10 +1076,10 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.004957</v>
+        <v>0.006687</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0059</v>
+        <v>0.009436999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1150,10 +1138,10 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007798</v>
+        <v>0.011015</v>
       </c>
       <c r="T11" t="n">
-        <v>0.007652</v>
+        <v>0.011661</v>
       </c>
     </row>
     <row r="12">
@@ -1212,10 +1200,10 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.002769</v>
+        <v>0.00621</v>
       </c>
       <c r="T12" t="n">
-        <v>0.002804</v>
+        <v>0.004445</v>
       </c>
     </row>
     <row r="13">
@@ -1274,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.000255</v>
+        <v>0.00042</v>
       </c>
       <c r="T13" t="n">
-        <v>0.000957</v>
+        <v>0.001433</v>
       </c>
     </row>
     <row r="14">
@@ -1338,10 +1326,10 @@
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.013571</v>
+        <v>0.017144</v>
       </c>
       <c r="T14" t="n">
-        <v>0.012532</v>
+        <v>0.017023</v>
       </c>
     </row>
     <row r="15">
@@ -1400,10 +1388,10 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.033848</v>
+        <v>0.051563</v>
       </c>
       <c r="T15" t="n">
-        <v>0.031433</v>
+        <v>0.051123</v>
       </c>
     </row>
     <row r="16">
@@ -1462,10 +1450,10 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.020872</v>
+        <v>0.039095</v>
       </c>
       <c r="T16" t="n">
-        <v>0.021624</v>
+        <v>0.042512</v>
       </c>
     </row>
     <row r="17">
@@ -1524,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.004406</v>
+        <v>0.006829</v>
       </c>
       <c r="T17" t="n">
-        <v>0.007065</v>
+        <v>0.012769</v>
       </c>
     </row>
     <row r="18">
@@ -1588,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06802</v>
+        <v>0.118095</v>
       </c>
       <c r="T18" t="n">
-        <v>0.068006</v>
+        <v>0.105609</v>
       </c>
     </row>
     <row r="19">
@@ -1650,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.493135</v>
+        <v>0.842948</v>
       </c>
       <c r="T19" t="n">
-        <v>0.511303</v>
+        <v>0.76847</v>
       </c>
     </row>
     <row r="20">
@@ -1712,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.832705</v>
+        <v>1.421245</v>
       </c>
       <c r="T20" t="n">
-        <v>0.837001</v>
+        <v>1.394324</v>
       </c>
     </row>
     <row r="21">
@@ -1774,10 +1762,10 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.478086</v>
+        <v>0.799215</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5725209999999999</v>
+        <v>0.929766</v>
       </c>
     </row>
     <row r="22">
@@ -1838,10 +1826,10 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.027538</v>
+        <v>0.039211</v>
       </c>
       <c r="T22" t="n">
-        <v>0.029341</v>
+        <v>0.046015</v>
       </c>
     </row>
     <row r="23">
@@ -1900,10 +1888,10 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.169993</v>
+        <v>0.193481</v>
       </c>
       <c r="T23" t="n">
-        <v>0.146481</v>
+        <v>0.193869</v>
       </c>
     </row>
     <row r="24">
@@ -1962,10 +1950,10 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.165392</v>
+        <v>0.229426</v>
       </c>
       <c r="T24" t="n">
-        <v>0.166558</v>
+        <v>0.21927</v>
       </c>
     </row>
     <row r="25">
@@ -2024,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.06751500000000001</v>
+        <v>0.077003</v>
       </c>
       <c r="T25" t="n">
-        <v>0.063357</v>
+        <v>0.108549</v>
       </c>
     </row>
     <row r="26">
@@ -2088,10 +2076,10 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.011513</v>
+        <v>0.015095</v>
       </c>
       <c r="T26" t="n">
-        <v>0.008751</v>
+        <v>0.013888</v>
       </c>
     </row>
     <row r="27">
@@ -2150,10 +2138,10 @@
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0254</v>
+        <v>0.038185</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02627</v>
+        <v>0.037752</v>
       </c>
     </row>
     <row r="28">
@@ -2212,10 +2200,10 @@
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.018127</v>
+        <v>0.029196</v>
       </c>
       <c r="T28" t="n">
-        <v>0.019217</v>
+        <v>0.025572</v>
       </c>
     </row>
     <row r="29">
@@ -2274,10 +2262,10 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.003559</v>
+        <v>0.006818</v>
       </c>
       <c r="T29" t="n">
-        <v>0.007538</v>
+        <v>0.011742</v>
       </c>
     </row>
     <row r="30">
@@ -2338,10 +2326,10 @@
         <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.086066</v>
+        <v>0.112418</v>
       </c>
       <c r="T30" t="n">
-        <v>0.073116</v>
+        <v>0.117233</v>
       </c>
     </row>
     <row r="31">
@@ -2400,10 +2388,10 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.495651</v>
+        <v>0.828345</v>
       </c>
       <c r="T31" t="n">
-        <v>0.49676</v>
+        <v>0.778569</v>
       </c>
     </row>
     <row r="32">
@@ -2462,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.832722</v>
+        <v>1.456496</v>
       </c>
       <c r="T32" t="n">
-        <v>0.822361</v>
+        <v>1.349547</v>
       </c>
     </row>
     <row r="33">
@@ -2524,10 +2512,10 @@
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.472905</v>
+        <v>0.838068</v>
       </c>
       <c r="T33" t="n">
-        <v>0.550743</v>
+        <v>1.06871</v>
       </c>
     </row>
   </sheetData>
